--- a/artfynd/A 6118-2025 artfynd.xlsx
+++ b/artfynd/A 6118-2025 artfynd.xlsx
@@ -1969,7 +1969,7 @@
         <v>125817491</v>
       </c>
       <c r="B15" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 6118-2025 artfynd.xlsx
+++ b/artfynd/A 6118-2025 artfynd.xlsx
@@ -1969,7 +1969,7 @@
         <v>125817491</v>
       </c>
       <c r="B15" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 6118-2025 artfynd.xlsx
+++ b/artfynd/A 6118-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125695698</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>125695696</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>125695699</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>125695697</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 6118-2025 artfynd.xlsx
+++ b/artfynd/A 6118-2025 artfynd.xlsx
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125695696</v>
+        <v>125695693</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>786633</v>
+        <v>786636</v>
       </c>
       <c r="R7" t="n">
-        <v>7361520</v>
+        <v>7361425</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1241,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125695693</v>
+        <v>125695696</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>786636</v>
+        <v>786633</v>
       </c>
       <c r="R8" t="n">
-        <v>7361425</v>
+        <v>7361520</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1338,11 +1343,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 6118-2025 artfynd.xlsx
+++ b/artfynd/A 6118-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125695698</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125695693</v>
+        <v>125695696</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>786636</v>
+        <v>786633</v>
       </c>
       <c r="R7" t="n">
-        <v>7361425</v>
+        <v>7361520</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1241,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125695696</v>
+        <v>125695693</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>786633</v>
+        <v>786636</v>
       </c>
       <c r="R8" t="n">
-        <v>7361520</v>
+        <v>7361425</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1343,6 +1338,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1673,7 +1673,7 @@
         <v>125695699</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>125695697</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>125817491</v>
       </c>
       <c r="B15" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 6118-2025 artfynd.xlsx
+++ b/artfynd/A 6118-2025 artfynd.xlsx
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125695696</v>
+        <v>125695693</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>786633</v>
+        <v>786636</v>
       </c>
       <c r="R7" t="n">
-        <v>7361520</v>
+        <v>7361425</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1241,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125695693</v>
+        <v>125695696</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>786636</v>
+        <v>786633</v>
       </c>
       <c r="R8" t="n">
-        <v>7361425</v>
+        <v>7361520</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1338,11 +1343,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 6118-2025 artfynd.xlsx
+++ b/artfynd/A 6118-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125695685</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125695698</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125695691</v>
       </c>
       <c r="B4" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>125695683</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>125695689</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>125695693</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>125695696</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>125695686</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>125695692</v>
       </c>
       <c r="B10" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>125695694</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>125695699</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>125695703</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>125695697</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>125817491</v>
       </c>
       <c r="B15" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 6118-2025 artfynd.xlsx
+++ b/artfynd/A 6118-2025 artfynd.xlsx
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125695693</v>
+        <v>125695696</v>
       </c>
       <c r="B7" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>786636</v>
+        <v>786633</v>
       </c>
       <c r="R7" t="n">
-        <v>7361425</v>
+        <v>7361520</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1241,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125695696</v>
+        <v>125695693</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>786633</v>
+        <v>786636</v>
       </c>
       <c r="R8" t="n">
-        <v>7361520</v>
+        <v>7361425</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1343,6 +1338,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1969,7 +1969,7 @@
         <v>125817491</v>
       </c>
       <c r="B15" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 6118-2025 artfynd.xlsx
+++ b/artfynd/A 6118-2025 artfynd.xlsx
@@ -1969,7 +1969,7 @@
         <v>125817491</v>
       </c>
       <c r="B15" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 6118-2025 artfynd.xlsx
+++ b/artfynd/A 6118-2025 artfynd.xlsx
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125695696</v>
+        <v>125695693</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>786633</v>
+        <v>786636</v>
       </c>
       <c r="R7" t="n">
-        <v>7361520</v>
+        <v>7361425</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1241,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125695693</v>
+        <v>125695696</v>
       </c>
       <c r="B8" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>786636</v>
+        <v>786633</v>
       </c>
       <c r="R8" t="n">
-        <v>7361425</v>
+        <v>7361520</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1338,11 +1343,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 6118-2025 artfynd.xlsx
+++ b/artfynd/A 6118-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125695685</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125695698</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125695691</v>
       </c>
       <c r="B4" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>125695683</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>125695689</v>
       </c>
       <c r="B6" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>125695693</v>
       </c>
       <c r="B7" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>125695696</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>125695686</v>
       </c>
       <c r="B9" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>125695692</v>
       </c>
       <c r="B10" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>125695694</v>
       </c>
       <c r="B11" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>125695699</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>125695703</v>
       </c>
       <c r="B13" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>125695697</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>125817491</v>
       </c>
       <c r="B15" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 6118-2025 artfynd.xlsx
+++ b/artfynd/A 6118-2025 artfynd.xlsx
@@ -1670,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125695699</v>
+        <v>125695703</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>786546</v>
+        <v>786672</v>
       </c>
       <c r="R12" t="n">
-        <v>7361613</v>
+        <v>7361447</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1741,6 +1741,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Bohål tre stycken på gammal tall och ringhack ammal tall och</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1767,10 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125695703</v>
+        <v>125695699</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1778,21 +1783,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1802,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>786672</v>
+        <v>786546</v>
       </c>
       <c r="R13" t="n">
-        <v>7361447</v>
+        <v>7361613</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1838,11 +1843,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Bohål tre stycken på gammal tall och ringhack ammal tall och</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 6118-2025 artfynd.xlsx
+++ b/artfynd/A 6118-2025 artfynd.xlsx
@@ -1969,7 +1969,7 @@
         <v>125817491</v>
       </c>
       <c r="B15" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 6118-2025 artfynd.xlsx
+++ b/artfynd/A 6118-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125695685</v>
+        <v>125695696</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>786569</v>
+        <v>786633</v>
       </c>
       <c r="R2" t="n">
-        <v>7361570</v>
+        <v>7361520</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125695698</v>
+        <v>125695697</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>786641</v>
+        <v>786612</v>
       </c>
       <c r="R3" t="n">
-        <v>7361384</v>
+        <v>7361456</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125695691</v>
+        <v>125695698</v>
       </c>
       <c r="B4" t="n">
-        <v>57653</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>786649</v>
+        <v>786641</v>
       </c>
       <c r="R4" t="n">
-        <v>7361390</v>
+        <v>7361384</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125695683</v>
+        <v>125695699</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>786628</v>
+        <v>786546</v>
       </c>
       <c r="R5" t="n">
-        <v>7361391</v>
+        <v>7361613</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1042,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,27 +1063,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125695689</v>
+        <v>125695691</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1108,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>786621</v>
+        <v>786649</v>
       </c>
       <c r="R6" t="n">
-        <v>7361436</v>
+        <v>7361390</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1170,27 +1160,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125695693</v>
+        <v>125695692</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1205,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>786636</v>
+        <v>786662</v>
       </c>
       <c r="R7" t="n">
-        <v>7361425</v>
+        <v>7361376</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1245,7 +1235,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack vid rot på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125695696</v>
+        <v>125695683</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>786633</v>
+        <v>786628</v>
       </c>
       <c r="R8" t="n">
-        <v>7361520</v>
+        <v>7361391</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1343,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Avskalad gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125695686</v>
+        <v>125695685</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>786610</v>
+        <v>786569</v>
       </c>
       <c r="R9" t="n">
-        <v>7361518</v>
+        <v>7361570</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1440,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,10 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125695692</v>
+        <v>125695686</v>
       </c>
       <c r="B10" t="n">
-        <v>57653</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,16 +1477,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>786662</v>
+        <v>786610</v>
       </c>
       <c r="R10" t="n">
-        <v>7361376</v>
+        <v>7361518</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1537,11 +1537,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack vid rot på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125695694</v>
+        <v>125695688</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>786637</v>
+        <v>786490</v>
       </c>
       <c r="R11" t="n">
-        <v>7361416</v>
+        <v>7361604</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1639,11 +1634,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1670,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125695703</v>
+        <v>125695689</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>786672</v>
+        <v>786621</v>
       </c>
       <c r="R12" t="n">
-        <v>7361447</v>
+        <v>7361436</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1741,11 +1731,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Bohål tre stycken på gammal tall och ringhack ammal tall och</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1772,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125695699</v>
+        <v>125695693</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1807,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>786546</v>
+        <v>786636</v>
       </c>
       <c r="R13" t="n">
-        <v>7361613</v>
+        <v>7361425</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1843,6 +1828,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1869,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125695697</v>
+        <v>125695694</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>786612</v>
+        <v>786637</v>
       </c>
       <c r="R14" t="n">
-        <v>7361456</v>
+        <v>7361416</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1940,6 +1930,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1966,10 +1961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125817491</v>
+        <v>125695703</v>
       </c>
       <c r="B15" t="n">
-        <v>91263</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,21 +1972,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,13 +1996,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>786589</v>
+        <v>786672</v>
       </c>
       <c r="R15" t="n">
-        <v>7361559</v>
+        <v>7361447</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2037,6 +2032,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Bohål tre stycken på gammal tall och ringhack ammal tall och</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 6118-2025 artfynd.xlsx
+++ b/artfynd/A 6118-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125695696</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125695697</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125695698</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125695699</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125695691</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125695692</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125695683</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1463,6 +1503,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125695685</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,6 +1605,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125695686</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1657,6 +1707,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125695688</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1754,6 +1809,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125695689</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125695693</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1958,6 +2023,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125695694</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2060,8 +2130,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125695703</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>